--- a/outputs/evaluation/architecture/design/v4/CF_M08/run_2/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v4/CF_M08/run_2/CF_M08_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.8643</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -589,10 +591,8 @@
           <t>fixedType</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1235,14 +1235,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1261,14 +1258,11 @@
       <c r="P2" t="n">
         <v>66</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1289,7 +1283,6 @@
       <c r="D3" t="n">
         <v>0.8608</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1310,7 +1303,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_22</t>
@@ -1321,7 +1313,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1340,7 +1331,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1371,7 +1361,6 @@
       <c r="D4" t="n">
         <v>0.8678</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1392,7 +1381,6 @@
           <t>['AU_03', 'AU_09']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1403,7 +1391,6 @@
           <t>system service, authentication service</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1422,7 +1409,6 @@
           <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_AU25</t>
@@ -1473,14 +1459,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1499,14 +1482,11 @@
       <c r="P5" t="n">
         <v>67</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1552,13 +1532,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Authentication</t>
@@ -1582,13 +1560,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1634,13 +1610,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Email</t>
@@ -1664,13 +1638,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1716,13 +1688,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Analytics</t>
@@ -1746,13 +1716,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1798,13 +1766,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Error monitoring</t>
@@ -1828,13 +1794,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1880,13 +1844,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Payment processing</t>
@@ -1910,13 +1872,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1962,13 +1922,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Cloud storage</t>
@@ -1992,13 +1950,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2039,14 +1995,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -2065,14 +2018,11 @@
       <c r="P12" t="n">
         <v>66</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2113,14 +2063,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -2144,13 +2091,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2196,13 +2141,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>React</t>
@@ -2226,13 +2169,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2278,13 +2219,11 @@
           <t>['AU_19', 'AU_28']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Brevo</t>
@@ -2308,13 +2247,11 @@
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU21</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2355,14 +2292,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -2386,13 +2320,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2438,13 +2370,11 @@
           <t>['AU_17', 'AU_27']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Sentry</t>
@@ -2468,13 +2398,11 @@
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M08_AU19</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2520,13 +2448,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -2550,13 +2476,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2602,13 +2526,11 @@
           <t>['AU_09', 'AU_23']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Google</t>
@@ -2632,13 +2554,11 @@
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M08_AU11</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2684,13 +2604,11 @@
           <t>['AU_11', 'AU_24']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2714,13 +2632,11 @@
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M08_AU13</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2766,13 +2682,11 @@
           <t>['AU_13', 'AU_25']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Stripe</t>
@@ -2796,13 +2710,11 @@
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M08_AU15</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2843,14 +2755,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2869,14 +2778,11 @@
       <c r="P22" t="n">
         <v>41</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2922,13 +2828,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -2952,13 +2856,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2999,14 +2901,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -3030,13 +2929,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3082,13 +2979,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -3112,13 +3007,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3164,13 +3057,11 @@
           <t>['AU_15', 'AU_26']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Google Analytics</t>
@@ -3194,13 +3085,11 @@
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3246,13 +3135,11 @@
           <t>['AU_03', 'AU_22']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -3276,13 +3163,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3351,7 +3236,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -3387,7 +3271,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>system service, cloud storage service</t>
@@ -3423,7 +3306,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>system service, payment processing service</t>
@@ -3459,7 +3341,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>system service, analytics service</t>
@@ -3495,7 +3376,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>system service, error monitoring service</t>
@@ -3511,7 +3391,6 @@
           <t>CF_M08_AU25</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.7498</v>
       </c>
@@ -3527,7 +3406,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>system service, email service</t>
@@ -3543,7 +3421,6 @@
           <t>CF_M08_AU25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0.7362</v>
       </c>
@@ -3559,7 +3436,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>data service, prisma</t>
@@ -3575,7 +3451,6 @@
           <t>CF_M08_AU24</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0.7562</v>
       </c>
@@ -3652,7 +3527,6 @@
           <t>Amazon EC2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>These services run on Amazon EC2 instances</t>
@@ -3688,7 +3562,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Each of these services is contained in a Docker container</t>
@@ -3724,7 +3597,6 @@
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>HTTPS, which is the standard for secure communications on the web</t>
@@ -3735,7 +3607,6 @@
           <t>AU_21</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7185</v>
       </c>
@@ -3756,7 +3627,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -3767,7 +3637,6 @@
           <t>AU_22</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.7153</v>
       </c>
@@ -3788,7 +3657,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
